--- a/fixErrorAllergyCode/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/fixErrorAllergyCode/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:38:14+00:00</t>
+    <t>2026-03-30T14:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
